--- a/resources/templates/standard/L2300-03.xlsx
+++ b/resources/templates/standard/L2300-03.xlsx
@@ -11,7 +11,10 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
+  <si>
+    <t>{{companyLogo}}</t>
+  </si>
   <si>
     <t>한도견본 기준서</t>
   </si>
@@ -519,12 +522,14 @@
   </cols>
   <sheetData>
     <row r="1" ht="20.1" customHeight="1" spans="1:48" x14ac:dyDescent="0.25">
-      <c r="A1" s="1"/>
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
       <c r="D1" s="1"/>
       <c r="E1" s="2" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F1" s="2"/>
       <c r="G1" s="2"/>
@@ -559,21 +564,21 @@
       <c r="AJ1" s="2"/>
       <c r="AK1" s="2"/>
       <c r="AL1" s="3" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AM1" s="3"/>
       <c r="AN1" s="4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AO1" s="4"/>
       <c r="AP1" s="4"/>
       <c r="AQ1" s="4" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AR1" s="4"/>
       <c r="AS1" s="4"/>
       <c r="AT1" s="4" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AU1" s="4"/>
       <c r="AV1" s="4"/>
@@ -680,7 +685,7 @@
     </row>
     <row r="4" ht="20.1" customHeight="1" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A4" s="6" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B4" s="6"/>
       <c r="C4" s="6"/>
@@ -694,7 +699,7 @@
       <c r="K4" s="7"/>
       <c r="L4" s="7"/>
       <c r="M4" s="4" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="N4" s="4"/>
       <c r="O4" s="4"/>
@@ -708,7 +713,7 @@
       <c r="W4" s="7"/>
       <c r="X4" s="7"/>
       <c r="Y4" s="4" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Z4" s="4"/>
       <c r="AA4" s="4"/>
@@ -722,7 +727,7 @@
       <c r="AI4" s="7"/>
       <c r="AJ4" s="7"/>
       <c r="AK4" s="4" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AL4" s="4"/>
       <c r="AM4" s="4"/>
@@ -738,7 +743,7 @@
     </row>
     <row r="5" ht="20.1" customHeight="1" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A5" s="8" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B5" s="8"/>
       <c r="C5" s="8"/>
@@ -756,7 +761,7 @@
       <c r="O5" s="8"/>
       <c r="P5" s="8"/>
       <c r="Q5" s="9" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="R5" s="9"/>
       <c r="S5" s="9"/>
